--- a/Data Analysis/VLOOKUP.xlsx
+++ b/Data Analysis/VLOOKUP.xlsx
@@ -866,7 +866,7 @@
         <v>4</v>
       </c>
       <c r="L4" s="19" t="str">
-        <f t="shared" ref="L4:L12" si="0">VLOOKUP(J4,$B$2:$E$12,2,FALSE)</f>
+        <f t="shared" ref="L4:L10" si="0">VLOOKUP(J4,$B$2:$E$12,2,FALSE)</f>
         <v>Wireless Mouse</v>
       </c>
     </row>

--- a/Data Analysis/VLOOKUP.xlsx
+++ b/Data Analysis/VLOOKUP.xlsx
@@ -188,6 +188,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -201,7 +202,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -228,28 +229,103 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -258,109 +334,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -373,9 +359,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -386,12 +394,23 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -399,37 +418,81 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -439,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -451,55 +514,199 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -510,6 +717,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B2:E12" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="B2:E12"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Product_ID" dataDxfId="6"/>
+    <tableColumn id="2" name="Product_Name" dataDxfId="5"/>
+    <tableColumn id="3" name="Category " dataDxfId="4"/>
+    <tableColumn id="4" name="Price" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -778,72 +998,72 @@
   <dimension ref="B1:L12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
     <col min="3" max="3" width="20.453125" customWidth="1"/>
     <col min="4" max="4" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="8.1796875" style="8" customWidth="1"/>
     <col min="9" max="10" width="10.7265625" customWidth="1"/>
     <col min="12" max="12" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="29" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="19" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="22">
         <v>24.99</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="16">
         <v>2</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="11" t="str">
         <f>VLOOKUP(J3,$B$2:$E$12,2,FALSE)</f>
         <v>Running Shoes</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -852,7 +1072,7 @@
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="23">
         <v>49.99</v>
       </c>
       <c r="H4" s="2"/>
@@ -862,16 +1082,16 @@
       <c r="J4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="15">
         <v>4</v>
       </c>
-      <c r="L4" s="19" t="str">
+      <c r="L4" s="12" t="str">
         <f t="shared" ref="L4:L10" si="0">VLOOKUP(J4,$B$2:$E$12,2,FALSE)</f>
         <v>Wireless Mouse</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -880,7 +1100,7 @@
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="23">
         <v>79.989999999999995</v>
       </c>
       <c r="H5" s="2"/>
@@ -890,16 +1110,16 @@
       <c r="J5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K5" s="15">
         <v>1</v>
       </c>
-      <c r="L5" s="19" t="str">
+      <c r="L5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wireless Mouse</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -908,7 +1128,7 @@
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="23">
         <v>12.5</v>
       </c>
       <c r="H6" s="2"/>
@@ -918,16 +1138,16 @@
       <c r="J6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="15">
         <v>9</v>
       </c>
-      <c r="L6" s="19" t="str">
+      <c r="L6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Bluetooth Speaker</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -936,7 +1156,7 @@
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="23">
         <v>149.99</v>
       </c>
       <c r="H7" s="2"/>
@@ -946,16 +1166,16 @@
       <c r="J7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="15">
         <v>6</v>
       </c>
-      <c r="L7" s="19" t="str">
+      <c r="L7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Running Shoes</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -964,7 +1184,7 @@
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="23">
         <v>39.99</v>
       </c>
       <c r="H8" s="2"/>
@@ -974,16 +1194,16 @@
       <c r="J8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="15">
         <v>4</v>
       </c>
-      <c r="L8" s="19" t="str">
+      <c r="L8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>LED Desk Lamp</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="21" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -992,7 +1212,7 @@
       <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="23">
         <v>29.99</v>
       </c>
       <c r="H9" s="2"/>
@@ -1002,16 +1222,16 @@
       <c r="J9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="15">
         <v>7</v>
       </c>
-      <c r="L9" s="19" t="str">
+      <c r="L9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Smartphone Stand</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1020,7 +1240,7 @@
       <c r="D10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="23">
         <v>18.75</v>
       </c>
       <c r="H10" s="2"/>
@@ -1030,16 +1250,16 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="15">
         <v>2</v>
       </c>
-      <c r="L10" s="19" t="str">
+      <c r="L10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wireless Mouse</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="21" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1048,7 +1268,7 @@
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="23">
         <v>14.99</v>
       </c>
       <c r="H11" s="2"/>
@@ -1058,38 +1278,38 @@
       <c r="J11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="15">
         <v>7</v>
       </c>
-      <c r="L11" s="19" t="str">
+      <c r="L11" s="12" t="str">
         <f>_xlfn.IFNA(VLOOKUP($J$11,$B$2:$E$12,2,FALSE),"Not Present")</f>
         <v>Not Present</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="26">
         <v>89.99</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="17">
         <v>3</v>
       </c>
-      <c r="L12" s="21" t="str">
+      <c r="L12" s="14" t="str">
         <f>_xlfn.IFNA(VLOOKUP(J12,$B$2:$E$12,2,FALSE),"Not Present")</f>
         <v>Not Present</v>
       </c>
@@ -1097,5 +1317,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>